--- a/src/inputs_data/data_entry.xlsx
+++ b/src/inputs_data/data_entry.xlsx
@@ -1,32 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MatíasFernández\Desktop\Simulacion Blue Express\src\inputs_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2FEEA31-6D32-433F-A298-9E7C8AB33646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03F0736-2EA1-4F8C-8CD9-9878EB717BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-120" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{27C3677B-1420-4A59-9C46-7E8D703566E7}"/>
+    <workbookView xWindow="-23148" yWindow="-120" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="destination_distribution" sheetId="3" r:id="rId1"/>
-    <sheet name="destination_to_exit" sheetId="4" r:id="rId2"/>
-    <sheet name="segment_distribution_by_dest" sheetId="5" r:id="rId3"/>
-    <sheet name="travel_receiving_to_exit" sheetId="7" r:id="rId4"/>
-    <sheet name="travel_exit_to_return" sheetId="8" r:id="rId5"/>
+    <sheet name="destination_distribution" sheetId="1" r:id="rId1"/>
+    <sheet name="destination_to_exit" sheetId="2" r:id="rId2"/>
+    <sheet name="segment_distribution_by_dest" sheetId="3" r:id="rId3"/>
+    <sheet name="travel_receiving_to_exit" sheetId="4" r:id="rId4"/>
+    <sheet name="travel_exit_to_return" sheetId="5" r:id="rId5"/>
+    <sheet name="board_geometry" sheetId="6" r:id="rId6"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">segment_distribution_by_dest!$A$1:$C$329</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -38,19 +33,124 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="176">
+  <si>
+    <t>exit_id</t>
+  </si>
+  <si>
+    <t>travel_distance_m</t>
+  </si>
+  <si>
+    <t>EXIT_1</t>
+  </si>
+  <si>
+    <t>EXIT_2</t>
+  </si>
+  <si>
+    <t>EXIT_3</t>
+  </si>
+  <si>
+    <t>EXIT_4</t>
+  </si>
+  <si>
+    <t>EXIT_5</t>
+  </si>
+  <si>
+    <t>EXIT_6</t>
+  </si>
+  <si>
+    <t>EXIT_7</t>
+  </si>
+  <si>
+    <t>EXIT_8</t>
+  </si>
+  <si>
+    <t>EXIT_9</t>
+  </si>
+  <si>
+    <t>EXIT_10</t>
+  </si>
+  <si>
+    <t>EXIT_11</t>
+  </si>
+  <si>
+    <t>EXIT_12</t>
+  </si>
+  <si>
+    <t>EXIT_13</t>
+  </si>
+  <si>
+    <t>EXIT_14</t>
+  </si>
+  <si>
+    <t>EXIT_15</t>
+  </si>
+  <si>
+    <t>EXIT_16</t>
+  </si>
+  <si>
+    <t>EXIT_17</t>
+  </si>
+  <si>
+    <t>EXIT_18</t>
+  </si>
+  <si>
+    <t>EXIT_19</t>
+  </si>
+  <si>
+    <t>EXIT_20</t>
+  </si>
+  <si>
+    <t>EXIT_21</t>
+  </si>
+  <si>
+    <t>EXIT_22</t>
+  </si>
+  <si>
+    <t>EXIT_23</t>
+  </si>
+  <si>
+    <t>EXIT_24</t>
+  </si>
+  <si>
+    <t>EXIT_25</t>
+  </si>
+  <si>
+    <t>EXIT_26</t>
+  </si>
+  <si>
+    <t>EXIT_27</t>
+  </si>
+  <si>
+    <t>EXIT_28</t>
+  </si>
+  <si>
+    <t>EXIT_29</t>
+  </si>
+  <si>
+    <t>EXIT_30</t>
+  </si>
+  <si>
+    <t>EXIT_31</t>
+  </si>
+  <si>
+    <t>EXIT_32</t>
+  </si>
   <si>
     <t>destination_id</t>
   </si>
   <si>
+    <t>probability</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
     <t>SCL 103</t>
   </si>
   <si>
@@ -282,103 +382,16 @@
     <t>PUNTA ARENAS</t>
   </si>
   <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>EXIT_1</t>
-  </si>
-  <si>
-    <t>EXIT_2</t>
-  </si>
-  <si>
-    <t>EXIT_3</t>
-  </si>
-  <si>
-    <t>EXIT_4</t>
-  </si>
-  <si>
-    <t>EXIT_5</t>
-  </si>
-  <si>
-    <t>EXIT_6</t>
-  </si>
-  <si>
-    <t>EXIT_7</t>
-  </si>
-  <si>
-    <t>EXIT_8</t>
-  </si>
-  <si>
-    <t>EXIT_9</t>
-  </si>
-  <si>
-    <t>EXIT_10</t>
-  </si>
-  <si>
-    <t>EXIT_11</t>
-  </si>
-  <si>
-    <t>EXIT_12</t>
-  </si>
-  <si>
-    <t>EXIT_13</t>
-  </si>
-  <si>
-    <t>EXIT_14</t>
-  </si>
-  <si>
-    <t>EXIT_15</t>
-  </si>
-  <si>
-    <t>EXIT_16</t>
-  </si>
-  <si>
-    <t>EXIT_17</t>
-  </si>
-  <si>
-    <t>EXIT_18</t>
-  </si>
-  <si>
-    <t>EXIT_19</t>
-  </si>
-  <si>
-    <t>EXIT_20</t>
-  </si>
-  <si>
-    <t>EXIT_21</t>
-  </si>
-  <si>
-    <t>EXIT_22</t>
-  </si>
-  <si>
-    <t>EXIT_23</t>
-  </si>
-  <si>
-    <t>EXIT_24</t>
-  </si>
-  <si>
-    <t>EXIT_25</t>
-  </si>
-  <si>
-    <t>EXIT_26</t>
-  </si>
-  <si>
-    <t>EXIT_27</t>
-  </si>
-  <si>
-    <t>EXIT_28</t>
-  </si>
-  <si>
-    <t>EXIT_29</t>
-  </si>
-  <si>
-    <t>EXIT_30</t>
-  </si>
-  <si>
-    <t>EXIT_31</t>
-  </si>
-  <si>
-    <t>EXIT_32</t>
+    <t>wing</t>
+  </si>
+  <si>
+    <t>upper</t>
+  </si>
+  <si>
+    <t>lower</t>
+  </si>
+  <si>
+    <t>segment</t>
   </si>
   <si>
     <t>Regular</t>
@@ -393,23 +406,173 @@
     <t>SuperBig</t>
   </si>
   <si>
-    <t>segment</t>
-  </si>
-  <si>
-    <t>probability</t>
-  </si>
-  <si>
-    <t>exit_id</t>
-  </si>
-  <si>
-    <t>travel_distance_m</t>
+    <t>parameter</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>d_reception_to_bifurcation_m</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Reception -&gt; bifurcacion inicial</t>
+  </si>
+  <si>
+    <t>n_turns_reception_to_bifurcation</t>
+  </si>
+  <si>
+    <t>turns</t>
+  </si>
+  <si>
+    <t>d_bifurcation_to_U_m</t>
+  </si>
+  <si>
+    <t>Bifurcacion -&gt; entrada carril U</t>
+  </si>
+  <si>
+    <t>n_turns_bifurcation_to_U</t>
+  </si>
+  <si>
+    <t>d_bifurcation_to_L_m</t>
+  </si>
+  <si>
+    <t>Bifurcacion -&gt; entrada carril L</t>
+  </si>
+  <si>
+    <t>n_turns_bifurcation_to_L</t>
+  </si>
+  <si>
+    <t>d_upper_m</t>
+  </si>
+  <si>
+    <t>Espaciamiento exits en U (observado)</t>
+  </si>
+  <si>
+    <t>d_lower_m</t>
+  </si>
+  <si>
+    <t>Espaciamiento exits en L (observado)</t>
+  </si>
+  <si>
+    <t>d_return_segment_upper_m</t>
+  </si>
+  <si>
+    <t>Espaciamiento puntos merge en R bajo ala upper</t>
+  </si>
+  <si>
+    <t>d_return_segment_lower_m</t>
+  </si>
+  <si>
+    <t>Espaciamiento puntos merge en R bajo ala lower</t>
+  </si>
+  <si>
+    <t>d_exit_off_U_m</t>
+  </si>
+  <si>
+    <t>Off-ramp: carril U -&gt; cola del exit upper</t>
+  </si>
+  <si>
+    <t>n_turns_exit_off_U</t>
+  </si>
+  <si>
+    <t>d_exit_off_L_m</t>
+  </si>
+  <si>
+    <t>Off-ramp: carril L -&gt; cola del exit lower</t>
+  </si>
+  <si>
+    <t>n_turns_exit_off_L</t>
+  </si>
+  <si>
+    <t>d_exit_on_U_m</t>
+  </si>
+  <si>
+    <t>On-ramp: exit upper -&gt; carril U (proxima parada en U)</t>
+  </si>
+  <si>
+    <t>n_turns_exit_on_U</t>
+  </si>
+  <si>
+    <t>d_exit_on_L_m</t>
+  </si>
+  <si>
+    <t>On-ramp: exit lower -&gt; carril L (proxima parada en L)</t>
+  </si>
+  <si>
+    <t>n_turns_exit_on_L</t>
+  </si>
+  <si>
+    <t>d_exit_on_R_m</t>
+  </si>
+  <si>
+    <t>On-ramp: exit -&gt; carril R (fin de ala o retorno)</t>
+  </si>
+  <si>
+    <t>n_turns_exit_on_R</t>
+  </si>
+  <si>
+    <t>pos_R_bifurcation_m</t>
+  </si>
+  <si>
+    <t>Posicion bifurcacion interna en R (0=cerca de Reception)</t>
+  </si>
+  <si>
+    <t>d_R_shortcut_to_L_m</t>
+  </si>
+  <si>
+    <t>Atajo: bifurcacion interna R -&gt; entrada carril L</t>
+  </si>
+  <si>
+    <t>n_turns_R_shortcut_to_L</t>
+  </si>
+  <si>
+    <t>Giros del atajo R-&gt;L</t>
+  </si>
+  <si>
+    <t>d_R_bifurcation_to_reception_m</t>
+  </si>
+  <si>
+    <t>Bifurcacion interna R -&gt; Reception</t>
+  </si>
+  <si>
+    <t>n_turns_R_bifurcation_to_reception</t>
+  </si>
+  <si>
+    <t>t_bifurcation_headway_s</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Headway minimo en bifurcacion inicial</t>
+  </si>
+  <si>
+    <t>t_merge_window_forward_s</t>
+  </si>
+  <si>
+    <t>Ventana adelante para reincorporarse a carril</t>
+  </si>
+  <si>
+    <t>t_merge_window_backward_s</t>
+  </si>
+  <si>
+    <t>Ventana atras para reincorporarse a carril</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -425,18 +588,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDDDDD"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -450,15 +621,18 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -793,32 +967,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5268DE70-6627-464E-A6C1-1F4490A8770F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M83"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1">
         <f>SUM(F2:F83)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2">
         <v>6.3897763578274758E-3</v>
@@ -828,9 +1002,9 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2">
         <v>6.3897763578274758E-3</v>
@@ -840,9 +1014,9 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2">
         <v>6.3897763578274758E-3</v>
@@ -852,45 +1026,45 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2">
-        <v>2.7215714116672583E-3</v>
+        <v>2.7215714116672579E-3</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2">
-        <v>2.7215714116672583E-3</v>
+        <v>2.7215714116672579E-3</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2">
-        <v>2.7215714116672583E-3</v>
+        <v>2.7215714116672579E-3</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2">
         <v>9.2296769613063514E-3</v>
@@ -900,9 +1074,9 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2">
         <v>7.0997515086971945E-4</v>
@@ -912,9 +1086,9 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2">
         <v>7.0997515086971945E-4</v>
@@ -924,21 +1098,21 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2">
-        <v>2.1299254526091584E-3</v>
+        <v>2.129925452609158E-3</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2">
         <v>3.9048633297834568E-3</v>
@@ -948,9 +1122,9 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2">
         <v>1.4199503017394389E-3</v>
@@ -960,9 +1134,9 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2">
         <v>6.0347887823926161E-3</v>
@@ -972,9 +1146,9 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2">
         <v>6.0347887823926161E-3</v>
@@ -984,9 +1158,9 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2">
         <v>5.6798012069577556E-3</v>
@@ -996,21 +1170,21 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2">
-        <v>2.4849130280440185E-3</v>
+        <v>2.484913028044019E-3</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2">
         <v>3.5498757543485972E-4</v>
@@ -1020,45 +1194,45 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2">
-        <v>3.5498757543485976E-3</v>
+        <v>3.549875754348598E-3</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2">
-        <v>1.7749378771742988E-3</v>
+        <v>1.774937877174299E-3</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B21" s="2">
-        <v>3.1948881789137375E-3</v>
+        <v>3.194888178913737E-3</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="B22" s="2">
         <v>7.0997515086971945E-4</v>
@@ -1068,9 +1242,9 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B23" s="2">
         <v>2.129925452609158E-3</v>
@@ -1080,9 +1254,9 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2">
         <v>1.064962726304579E-3</v>
@@ -1092,9 +1266,9 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="B25" s="2">
         <v>2.129925452609158E-3</v>
@@ -1104,9 +1278,9 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B26" s="2">
         <v>3.5498757543485972E-4</v>
@@ -1116,9 +1290,9 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B27" s="2">
         <v>1.064962726304579E-3</v>
@@ -1128,21 +1302,21 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B28" s="2">
-        <v>2.1299254526091584E-3</v>
+        <v>2.129925452609158E-3</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="B29" s="2">
         <v>3.9048633297834568E-3</v>
@@ -1152,9 +1326,9 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="B30" s="2">
         <v>2.129925452609158E-3</v>
@@ -1164,9 +1338,9 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="B31" s="2">
         <v>6.0347887823926152E-3</v>
@@ -1176,9 +1350,9 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B32" s="2">
         <v>2.8399006034788778E-3</v>
@@ -1188,21 +1362,21 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B33" s="2">
-        <v>3.5498757543485976E-3</v>
+        <v>3.549875754348598E-3</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="B34" s="2">
         <v>6.3897763578274758E-3</v>
@@ -1212,21 +1386,21 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B35" s="2">
-        <v>1.8459353922612706E-2</v>
+        <v>1.845935392261271E-2</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B36" s="2">
         <v>6.0347887823926152E-3</v>
@@ -1236,9 +1410,9 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B37" s="2">
         <v>3.9048633297834568E-3</v>
@@ -1248,9 +1422,9 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="B38" s="2">
         <v>5.3248136315228959E-3</v>
@@ -1260,9 +1434,9 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B39" s="2">
         <v>9.2296769613063531E-3</v>
@@ -1272,9 +1446,9 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B40" s="2">
         <v>9.2296769613063531E-3</v>
@@ -1284,9 +1458,9 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B41" s="2">
         <v>5.3248136315228959E-3</v>
@@ -1296,9 +1470,9 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="B42" s="2">
         <v>7.0997515086971951E-3</v>
@@ -1308,21 +1482,21 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B43" s="2">
-        <v>4.6148384806531766E-3</v>
+        <v>4.6148384806531774E-3</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B44" s="2">
         <v>5.5023074192403262E-3</v>
@@ -1332,9 +1506,9 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B45" s="2">
         <v>5.5023074192403262E-3</v>
@@ -1344,21 +1518,21 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B46" s="2">
-        <v>1.5619453319133827E-2</v>
+        <v>1.5619453319133831E-2</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B47" s="2">
         <v>6.3897763578274749E-3</v>
@@ -1368,9 +1542,9 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B48" s="2">
         <v>2.6624068157614479E-3</v>
@@ -1380,9 +1554,9 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B49" s="2">
         <v>2.6624068157614479E-3</v>
@@ -1392,9 +1566,9 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B50" s="2">
         <v>2.8399006034788778E-3</v>
@@ -1404,9 +1578,9 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B51" s="2">
         <v>4.2598509052183169E-3</v>
@@ -1416,9 +1590,9 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B52" s="2">
         <v>4.2598509052183169E-3</v>
@@ -1428,9 +1602,9 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="B53" s="2">
         <v>6.271447166015855E-3</v>
@@ -1440,9 +1614,9 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B54" s="2">
         <v>6.271447166015855E-3</v>
@@ -1452,9 +1626,9 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B55" s="2">
         <v>6.271447166015855E-3</v>
@@ -1464,9 +1638,9 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="B56" s="2">
         <v>5.3248136315228959E-3</v>
@@ -1476,9 +1650,9 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="B57" s="2">
         <v>1.4199503017394389E-3</v>
@@ -1488,9 +1662,9 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B58" s="2">
         <v>7.8097266595669136E-3</v>
@@ -1500,9 +1674,9 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B59" s="2">
         <v>1.419950301739439E-2</v>
@@ -1512,9 +1686,9 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="B60" s="2">
         <v>2.7689030883919059E-2</v>
@@ -1524,33 +1698,33 @@
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="B61" s="2">
-        <v>1.8814341498047567E-2</v>
+        <v>1.881434149804757E-2</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="B62" s="2">
-        <v>1.5974440894568686E-2</v>
+        <v>1.5974440894568689E-2</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="B63" s="2">
         <v>4.6503372381966619E-2</v>
@@ -1560,9 +1734,9 @@
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="B64" s="2">
         <v>9.2296769613063531E-3</v>
@@ -1572,9 +1746,9 @@
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="B65" s="2">
         <v>0</v>
@@ -1584,9 +1758,9 @@
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="B66" s="2">
         <v>3.6563720269790552E-2</v>
@@ -1596,9 +1770,9 @@
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B67" s="2">
         <v>4.2598509052183167E-2</v>
@@ -1608,9 +1782,9 @@
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="B68" s="2">
         <v>3.1948881789137372E-2</v>
@@ -1620,69 +1794,69 @@
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="B69" s="2">
-        <v>1.9169329073482424E-2</v>
+        <v>1.916932907348242E-2</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="B70" s="2">
-        <v>2.1654242101526444E-2</v>
+        <v>2.1654242101526441E-2</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="B71" s="2">
-        <v>5.0763223287184946E-2</v>
+        <v>5.0763223287184953E-2</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="B72" s="2">
-        <v>3.1238906638267654E-2</v>
+        <v>3.1238906638267651E-2</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="B73" s="2">
-        <v>5.5023074192403265E-2</v>
+        <v>5.5023074192403272E-2</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="B74" s="2">
         <v>3.1593894213702518E-2</v>
@@ -1692,9 +1866,9 @@
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="B75" s="2">
         <v>7.9872204472843447E-2</v>
@@ -1704,9 +1878,9 @@
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="B76" s="2">
         <v>3.549875754348597E-2</v>
@@ -1716,45 +1890,45 @@
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="B77" s="2">
-        <v>5.0763223287184946E-2</v>
+        <v>5.0763223287184953E-2</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="B78" s="2">
-        <v>1.7394391196308125E-2</v>
+        <v>1.7394391196308121E-2</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B79" s="2">
-        <v>2.1654242101526444E-2</v>
+        <v>2.1654242101526441E-2</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="B80" s="2">
         <v>4.7568335108271201E-2</v>
@@ -1764,33 +1938,33 @@
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="B81" s="2">
-        <v>1.4554490592829249E-2</v>
+        <v>1.4554490592829251E-2</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="B82" s="2">
-        <v>1.1714589989350372E-2</v>
+        <v>1.171458998935037E-2</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="B83" s="2">
         <v>6.7447639332623346E-3</v>
@@ -1801,678 +1975,929 @@
       <c r="F83" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4090214-1D9D-40AC-9987-9BDBCC532B1A}">
-  <dimension ref="A1:B83"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C83"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="10" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>76</v>
+      </c>
+      <c r="B43" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="B51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="B53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="B54" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B55" t="s">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="C55" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B56" t="s">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="C56" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>87</v>
+      </c>
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>88</v>
+      </c>
+      <c r="B58" t="s">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="C58" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>89</v>
+      </c>
+      <c r="B59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>90</v>
+      </c>
+      <c r="B60" t="s">
         <v>22</v>
       </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="C60" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>91</v>
+      </c>
+      <c r="B61" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>92</v>
+      </c>
+      <c r="B62" t="s">
         <v>23</v>
       </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="C62" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B63" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>94</v>
+      </c>
+      <c r="B64" t="s">
         <v>24</v>
       </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="C64" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>95</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>96</v>
+      </c>
+      <c r="B66" t="s">
         <v>25</v>
       </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="C66" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>97</v>
+      </c>
+      <c r="B67" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>98</v>
+      </c>
+      <c r="B68" t="s">
         <v>26</v>
       </c>
-      <c r="B28" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="C68" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>99</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>100</v>
+      </c>
+      <c r="B70" t="s">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="C70" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>101</v>
+      </c>
+      <c r="B71" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>102</v>
+      </c>
+      <c r="B72" t="s">
         <v>28</v>
       </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="C72" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>103</v>
+      </c>
+      <c r="B73" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>104</v>
+      </c>
+      <c r="B74" t="s">
         <v>29</v>
       </c>
-      <c r="B31" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="C74" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>105</v>
+      </c>
+      <c r="B75" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>106</v>
+      </c>
+      <c r="B76" t="s">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="C76" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>107</v>
+      </c>
+      <c r="B77" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>108</v>
+      </c>
+      <c r="B78" t="s">
         <v>31</v>
       </c>
-      <c r="B33" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="C78" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>109</v>
+      </c>
+      <c r="B79" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" t="s">
         <v>32</v>
       </c>
-      <c r="B34" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="C80" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>111</v>
+      </c>
+      <c r="B81" t="s">
+        <v>32</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>112</v>
+      </c>
+      <c r="B82" t="s">
         <v>33</v>
       </c>
-      <c r="B35" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>50</v>
-      </c>
-      <c r="B56" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>52</v>
-      </c>
-      <c r="B58" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>54</v>
-      </c>
-      <c r="B60" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>60</v>
-      </c>
-      <c r="B66" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B67" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>66</v>
-      </c>
-      <c r="B72" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>67</v>
-      </c>
-      <c r="B73" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>68</v>
-      </c>
-      <c r="B74" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>69</v>
-      </c>
-      <c r="B75" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>70</v>
-      </c>
-      <c r="B76" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>71</v>
-      </c>
-      <c r="B77" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>72</v>
-      </c>
-      <c r="B78" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>73</v>
-      </c>
-      <c r="B79" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>74</v>
-      </c>
-      <c r="B80" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>75</v>
-      </c>
-      <c r="B81" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>76</v>
-      </c>
-      <c r="B82" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C82" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="B83" t="s">
-        <v>110</v>
+        <v>33</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2481,3632 +2906,3632 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CCC63CD-5FB2-43A3-A64A-1A45111272DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C329"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C2" s="3">
-        <v>0.37037037037037035</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.37037037037037029</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C3" s="3">
-        <v>0.37037037037037035</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.37037037037037029</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C4" s="3">
-        <v>0.37037037037037035</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.37037037037037029</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C5" s="3">
         <v>0.30434782608695649</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C6" s="3">
         <v>0.30434782608695649</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C7" s="3">
         <v>0.30434782608695649</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C8" s="3">
-        <v>0.30769230769230765</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.30769230769230771</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C9" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C10" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C11" s="3">
-        <v>0.49999999999999994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.49999999999999989</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C12" s="3">
         <v>0.63636363636363635</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C13" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C14" s="3">
-        <v>0.47058823529411764</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.47058823529411759</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3">
         <v>0.29411764705882348</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3">
         <v>0.3125</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C17" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C18" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C19" s="3">
         <v>0.3</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C21" s="3">
-        <v>0.11111111111111109</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C22" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C23" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C24" s="3">
-        <v>0.33333333333333337</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.33333333333333343</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C25" s="3">
-        <v>0.33333333333333337</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.33333333333333343</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C26" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C27" s="3">
-        <v>0.33333333333333337</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.33333333333333343</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C28" s="3">
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C29" s="3">
-        <v>0.36363636363636365</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.36363636363636359</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C30" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C31" s="3">
         <v>0.3529411764705882</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C32" s="3">
-        <v>0.37499999999999994</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.37499999999999989</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C33" s="3">
-        <v>0.39999999999999997</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C34" s="3">
-        <v>0.44444444444444436</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C35" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C36" s="3">
-        <v>0.29411764705882354</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.29411764705882348</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C37" s="3">
         <v>0.45454545454545459</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C38" s="3">
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C39" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C40" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C41" s="3">
-        <v>0.26666666666666666</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.26666666666666672</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C42" s="3">
-        <v>0.44999999999999996</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C43" s="3">
         <v>0.46153846153846151</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C44" s="3">
-        <v>0.29032258064516125</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.29032258064516131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C45" s="3">
-        <v>0.29032258064516125</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.29032258064516131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C46" s="3">
         <v>0.22727272727272729</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C47" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B48" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C48" s="3">
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B49" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C49" s="3">
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C50" s="3">
-        <v>0.37499999999999994</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.37499999999999989</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C51" s="3">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C52" s="3">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="B53" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C53" s="3">
         <v>0.35849056603773582</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C54" s="3">
         <v>0.35849056603773582</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B55" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C55" s="3">
         <v>0.35849056603773582</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C56" s="3">
-        <v>0.26666666666666666</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.26666666666666672</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C57" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C58" s="3">
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C59" s="3">
         <v>0.17499999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="B60" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C60" s="3">
-        <v>0.28205128205128205</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.28205128205128199</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="B61" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C61" s="3">
         <v>0.56603773584905659</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="B62" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C62" s="3">
-        <v>0.39999999999999997</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="B63" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C63" s="3">
         <v>0.38931297709923668</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C64" s="3">
-        <v>0.19230769230769232</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.19230769230769229</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="B65" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C65" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="B66" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C66" s="3">
         <v>0.38834951456310679</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B67" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C67" s="3">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="B68" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C68" s="3">
         <v>0.27777777777777779</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="B69" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C69" s="3">
-        <v>0.46296296296296297</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.46296296296296302</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C70" s="3">
-        <v>0.21311475409836064</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.21311475409836059</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="B71" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C71" s="3">
         <v>0.39860139860139859</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="B72" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C72" s="3">
         <v>0.30681818181818182</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="B73" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C73" s="3">
         <v>0.25161290322580648</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="B74" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C74" s="3">
         <v>0.3707865168539326</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="B75" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C75" s="3">
-        <v>0.27999999999999997</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="B76" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C76" s="3">
         <v>0.27</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="B77" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C77" s="3">
-        <v>0.24475524475524474</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.24475524475524471</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="B78" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C78" s="3">
-        <v>0.38775510204081637</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.38775510204081642</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B79" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C79" s="3">
         <v>0.27868852459016391</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="B80" t="s">
+        <v>118</v>
+      </c>
+      <c r="C80" s="3">
+        <v>0.40298507462686572</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>111</v>
       </c>
-      <c r="C80" s="3">
-        <v>0.40298507462686567</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>75</v>
-      </c>
       <c r="B81" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C81" s="3">
         <v>0.3658536585365853</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C82" s="3">
         <v>0.27272727272727271</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="B83" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C83" s="3">
-        <v>0.26315789473684215</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.26315789473684209</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B84" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C84" s="3">
-        <v>0.11111111111111109</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B85" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C85" s="3">
-        <v>0.11111111111111109</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B86" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C86" s="3">
-        <v>0.11111111111111109</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B87" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C87" s="3">
-        <v>0.43478260869565216</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.43478260869565222</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C88" s="3">
-        <v>0.43478260869565216</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.43478260869565222</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="B89" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C89" s="3">
-        <v>0.43478260869565216</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.43478260869565222</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B90" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C90" s="3">
-        <v>0.23076923076923073</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.2307692307692307</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B91" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C91" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B92" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C92" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="B93" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C93" s="3">
-        <v>0.16666666666666666</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B94" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C94" s="3">
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B95" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C95" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C96" s="3">
-        <v>0.11764705882352941</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1176470588235294</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C97" s="3">
         <v>0.29411764705882348</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="B98" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C98" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B99" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C99" s="3">
         <v>0.2857142857142857</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="B100" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B101" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C101" s="3">
-        <v>0.19999999999999998</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B102" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C102" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B103" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C103" s="3">
-        <v>0.11111111111111109</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="B104" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C104" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B105" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C105" s="3">
-        <v>0.33333333333333337</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.33333333333333343</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="B106" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C106" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="B107" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C107" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B108" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C108" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B109" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C109" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B110" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C110" s="3">
-        <v>0.16666666666666666</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="B111" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C111" s="3">
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C112" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C113" s="3">
-        <v>5.8823529411764705E-2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+        <v>5.8823529411764712E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C114" s="3">
         <v>0.125</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B115" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C115" s="3">
-        <v>0.19999999999999998</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C116" s="3">
-        <v>0.16666666666666663</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1666666666666666</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B117" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C117" s="3">
         <v>9.6153846153846159E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B118" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C118" s="3">
         <v>0.41176470588235292</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B119" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C119" s="3">
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="B120" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C120" s="3">
-        <v>0.13333333333333333</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1333333333333333</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B121" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C121" s="3">
         <v>0.36538461538461542</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B122" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C122" s="3">
         <v>0.36538461538461542</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B123" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C123" s="3">
-        <v>0.19999999999999998</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="B124" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C124" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B125" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C125" s="3">
         <v>7.6923076923076927E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B126" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C126" s="3">
         <v>9.6774193548387094E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B127" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C127" s="3">
         <v>9.6774193548387094E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B128" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C128" s="3">
-        <v>0.29545454545454547</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.29545454545454553</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B129" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C129" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C130" s="3">
-        <v>0.13333333333333333</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1333333333333333</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B131" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C131" s="3">
-        <v>0.13333333333333333</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1333333333333333</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B132" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C132" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B133" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C133" s="3">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B134" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C134" s="3">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="B135" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C135" s="3">
-        <v>0.16981132075471697</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.169811320754717</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B136" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C136" s="3">
-        <v>0.16981132075471697</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.169811320754717</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B137" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C137" s="3">
-        <v>0.16981132075471697</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.169811320754717</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="B138" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C138" s="3">
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="B139" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C139" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B140" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C140" s="3">
-        <v>0.18181818181818182</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1818181818181818</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B141" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C141" s="3">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="B142" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C142" s="3">
-        <v>0.14102564102564102</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.141025641025641</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="B143" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C143" s="3">
         <v>0.13207547169811321</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="B144" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C144" s="3">
-        <v>0.13333333333333333</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1333333333333333</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="B145" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C145" s="3">
         <v>9.9236641221374058E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="B146" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C146" s="3">
         <v>7.6923076923076927E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="B147" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C147" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="B148" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C148" s="3">
         <v>0.1553398058252427</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B149" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C149" s="3">
-        <v>0.16666666666666666</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="B150" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C150" s="3">
-        <v>0.19999999999999998</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="B151" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C151" s="3">
         <v>9.2592592592592601E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="B152" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C152" s="3">
         <v>0.24590163934426229</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="B153" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C153" s="3">
-        <v>0.13286713286713286</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.13286713286713289</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="B154" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C154" s="3">
-        <v>0.18181818181818182</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1818181818181818</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="B155" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C155" s="3">
         <v>0.1032258064516129</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="B156" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C156" s="3">
-        <v>0.10112359550561797</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.101123595505618</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="B157" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C157" s="3">
-        <v>0.14666666666666667</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1466666666666667</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="B158" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C158" s="3">
-        <v>0.22000000000000003</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="B159" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C159" s="3">
-        <v>0.17482517482517482</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.17482517482517479</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="B160" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C160" s="3">
-        <v>0.24489795918367346</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.24489795918367349</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B161" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C161" s="3">
         <v>0.27868852459016391</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="B162" t="s">
+        <v>119</v>
+      </c>
+      <c r="C162" s="3">
+        <v>0.1119402985074627</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>111</v>
+      </c>
+      <c r="B163" t="s">
+        <v>119</v>
+      </c>
+      <c r="C163" s="3">
+        <v>0.26829268292682917</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
         <v>112</v>
       </c>
-      <c r="C162" s="3">
-        <v>0.11194029850746269</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>75</v>
-      </c>
-      <c r="B163" t="s">
-        <v>112</v>
-      </c>
-      <c r="C163" s="3">
-        <v>0.26829268292682923</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>76</v>
-      </c>
       <c r="B164" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C164" s="3">
-        <v>0.21212121212121213</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.2121212121212121</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="B165" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C165" s="3">
-        <v>0.15789473684210525</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.15789473684210531</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B166" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C166" s="3">
-        <v>0.24074074074074067</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.2407407407407407</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B167" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C167" s="3">
-        <v>0.24074074074074067</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.2407407407407407</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B168" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C168" s="3">
-        <v>0.24074074074074067</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.2407407407407407</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B169" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C169" s="3">
-        <v>0.13043478260869565</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.13043478260869559</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B170" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C170" s="3">
-        <v>0.13043478260869565</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.13043478260869559</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="B171" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C171" s="3">
-        <v>0.13043478260869565</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.13043478260869559</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B172" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C172" s="3">
-        <v>0.15384615384615383</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1538461538461538</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B173" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C173" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B174" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C174" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="B175" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C175" s="3">
-        <v>0.16666666666666666</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B176" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C176" s="3">
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B177" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C177" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B178" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C178" s="3">
-        <v>0.11764705882352941</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1176470588235294</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B179" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C179" s="3">
         <v>0.1176470588235294</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="B180" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C180" s="3">
         <v>0.4375</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B181" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C181" s="3">
         <v>0.42857142857142849</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="B182" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C182" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B183" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C183" s="3">
-        <v>0.19999999999999998</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B184" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C184" s="3">
-        <v>0.19999999999999998</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B185" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C185" s="3">
-        <v>0.44444444444444436</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="B186" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C186" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B187" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C187" s="3">
-        <v>0.16666666666666669</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="B188" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C188" s="3">
-        <v>0.33333333333333337</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.33333333333333343</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="B189" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C189" s="3">
-        <v>0.33333333333333337</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.33333333333333343</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B190" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C190" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B191" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C191" s="3">
-        <v>0.33333333333333337</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.33333333333333343</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B192" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C192" s="3">
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="B193" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C193" s="3">
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="B194" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C194" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="B195" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C195" s="3">
         <v>0.1764705882352941</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B196" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C196" s="3">
         <v>0.125</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B197" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C197" s="3">
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="B198" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C198" s="3">
-        <v>0.22222222222222218</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B199" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C199" s="3">
-        <v>0.23076923076923075</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.23076923076923081</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B200" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C200" s="3">
         <v>0.1764705882352941</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B201" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C201" s="3">
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="B202" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C202" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B203" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C203" s="3">
-        <v>0.15384615384615385</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.15384615384615391</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B204" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C204" s="3">
-        <v>0.15384615384615385</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.15384615384615391</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B205" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C205" s="3">
-        <v>0.26666666666666666</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.26666666666666672</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="B206" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C206" s="3">
         <v>0.3</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B207" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C207" s="3">
-        <v>0.23076923076923075</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.23076923076923081</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B208" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C208" s="3">
-        <v>0.25806451612903225</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.25806451612903231</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B209" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C209" s="3">
-        <v>0.25806451612903225</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.25806451612903231</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B210" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C210" s="3">
         <v>0.15909090909090909</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B211" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C211" s="3">
         <v>0.27777777777777779</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B212" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C212" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B213" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C213" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B214" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C214" s="3">
         <v>0.125</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B215" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C215" s="3">
-        <v>0.20833333333333331</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.20833333333333329</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B216" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C216" s="3">
-        <v>0.20833333333333331</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.20833333333333329</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="B217" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C217" s="3">
-        <v>0.22641509433962265</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.22641509433962259</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B218" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C218" s="3">
-        <v>0.22641509433962265</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.22641509433962259</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B219" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C219" s="3">
-        <v>0.22641509433962265</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.22641509433962259</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="B220" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C220" s="3">
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="B221" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C221" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B222" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C222" s="3">
         <v>0.27272727272727271</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B223" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C223" s="3">
-        <v>0.22499999999999998</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.22500000000000001</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="B224" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C224" s="3">
         <v>0.19230769230769229</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="B225" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C225" s="3">
         <v>0.13207547169811321</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="B226" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C226" s="3">
-        <v>0.15555555555555556</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.15555555555555561</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="B227" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C227" s="3">
-        <v>0.19847328244274812</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.19847328244274809</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="B228" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C228" s="3">
         <v>0.30769230769230771</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="B229" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C229" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="B230" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C230" s="3">
-        <v>0.17475728155339804</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.17475728155339801</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B231" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C231" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="B232" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C232" s="3">
-        <v>0.22222222222222224</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="B233" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C233" s="3">
         <v>0.1851851851851852</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="B234" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C234" s="3">
-        <v>0.29508196721311475</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.29508196721311469</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="B235" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C235" s="3">
         <v>0.1888111888111888</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="B236" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C236" s="3">
-        <v>0.20454545454545453</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.2045454545454545</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="B237" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C237" s="3">
-        <v>0.23225806451612901</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.23225806451612899</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="B238" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C238" s="3">
-        <v>0.16853932584269665</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.16853932584269671</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="B239" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C239" s="3">
-        <v>0.22222222222222224</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="B240" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C240" s="3">
-        <v>0.15000000000000002</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="B241" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C241" s="3">
-        <v>0.12587412587412586</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.12587412587412589</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="B242" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C242" s="3">
-        <v>6.1224489795918366E-2</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6.1224489795918373E-2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B243" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C243" s="3">
         <v>0.16393442622950821</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="B244" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C244" s="3">
-        <v>0.17164179104477612</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.17164179104477609</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="B245" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C245" s="3">
-        <v>0.19512195121951215</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.19512195121951209</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="B246" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C246" s="3">
         <v>9.0909090909090898E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="B247" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C247" s="3">
         <v>0.2105263157894737</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B248" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C248" s="3">
-        <v>0.27777777777777773</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.27777777777777768</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B249" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C249" s="3">
-        <v>0.27777777777777773</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.27777777777777768</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B250" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C250" s="3">
-        <v>0.27777777777777773</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.27777777777777768</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B251" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C251" s="3">
-        <v>0.13043478260869565</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.13043478260869559</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B252" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C252" s="3">
-        <v>0.13043478260869565</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.13043478260869559</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="B253" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C253" s="3">
-        <v>0.13043478260869565</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.13043478260869559</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B254" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C254" s="3">
-        <v>0.30769230769230765</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.30769230769230771</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B255" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C255" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B256" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C256" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="B257" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C257" s="3">
-        <v>0.16666666666666666</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B258" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C258" s="3">
-        <v>0.18181818181818182</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1818181818181818</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B259" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C259" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B260" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C260" s="3">
-        <v>0.29411764705882354</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.29411764705882348</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B261" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C261" s="3">
         <v>0.29411764705882348</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="B262" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C262" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B263" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C263" s="3">
         <v>0.2857142857142857</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="B264" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C264" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B265" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C265" s="3">
         <v>0.3</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B266" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C266" s="3">
         <v>0.79999999999999993</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B267" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C267" s="3">
-        <v>0.33333333333333326</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="B268" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C268" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B269" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C269" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="B270" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C270" s="3">
-        <v>0.33333333333333337</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.33333333333333343</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="B271" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C271" s="3">
-        <v>0.33333333333333337</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.33333333333333343</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B272" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C272" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B273" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C273" s="3">
-        <v>0.33333333333333337</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.33333333333333343</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B274" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C274" s="3">
-        <v>0.16666666666666666</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="B275" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C275" s="3">
         <v>0.45454545454545459</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="B276" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C276" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="B277" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C277" s="3">
         <v>0.41176470588235292</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B278" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C278" s="3">
-        <v>0.37499999999999994</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.37499999999999989</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B279" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C279" s="3">
         <v>0.3</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="B280" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C280" s="3">
-        <v>0.16666666666666663</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1666666666666666</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B281" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C281" s="3">
-        <v>0.17307692307692307</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1730769230769231</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B282" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C282" s="3">
-        <v>0.11764705882352941</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1176470588235294</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B283" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C283" s="3">
-        <v>0.36363636363636365</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.36363636363636359</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="B284" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C284" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B285" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C285" s="3">
-        <v>0.23076923076923075</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.23076923076923081</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B286" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C286" s="3">
-        <v>0.23076923076923075</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.23076923076923081</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B287" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C287" s="3">
-        <v>0.26666666666666666</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.26666666666666672</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="B288" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C288" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B289" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C289" s="3">
-        <v>0.23076923076923075</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.23076923076923081</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B290" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C290" s="3">
         <v>0.35483870967741932</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B291" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C291" s="3">
         <v>0.35483870967741932</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B292" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C292" s="3">
         <v>0.31818181818181818</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B293" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C293" s="3">
-        <v>0.22222222222222224</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B294" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C294" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B295" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C295" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B296" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C296" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B297" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C297" s="3">
-        <v>0.24999999999999997</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B298" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C298" s="3">
-        <v>0.24999999999999997</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="B299" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C299" s="3">
         <v>0.2452830188679245</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B300" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C300" s="3">
         <v>0.2452830188679245</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B301" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C301" s="3">
         <v>0.2452830188679245</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="B302" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C302" s="3">
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="B303" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C303" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B304" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C304" s="3">
         <v>0.45454545454545459</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B305" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C305" s="3">
         <v>0.52500000000000002</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="B306" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C306" s="3">
         <v>0.38461538461538458</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="B307" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C307" s="3">
-        <v>0.16981132075471697</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.169811320754717</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="B308" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C308" s="3">
         <v>0.31111111111111112</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="B309" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C309" s="3">
-        <v>0.31297709923664124</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.31297709923664119</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="B310" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C310" s="3">
         <v>0.42307692307692307</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="B311" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C311" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="B312" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C312" s="3">
         <v>0.28155339805825241</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B313" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C313" s="3">
-        <v>0.22499999999999998</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.22500000000000001</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="B314" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C314" s="3">
         <v>0.3</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="B315" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C315" s="3">
-        <v>0.25925925925925924</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.25925925925925919</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="B316" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C316" s="3">
         <v>0.24590163934426229</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="B317" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C317" s="3">
-        <v>0.27972027972027974</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.27972027972027969</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="B318" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C318" s="3">
         <v>0.30681818181818182</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="B319" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C319" s="3">
         <v>0.41290322580645161</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="B320" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C320" s="3">
         <v>0.3595505617977528</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="B321" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C321" s="3">
         <v>0.3511111111111111</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="B322" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C322" s="3">
         <v>0.36</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="B323" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C323" s="3">
-        <v>0.45454545454545453</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.45454545454545447</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="B324" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C324" s="3">
         <v>0.3061224489795919</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B325" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C325" s="3">
         <v>0.27868852459016391</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="B326" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C326" s="3">
-        <v>0.31343283582089554</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.31343283582089548</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="B327" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C327" s="3">
-        <v>0.17073170731707313</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.1707317073170731</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="B328" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C328" s="3">
-        <v>0.42424242424242425</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.42424242424242431</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="B329" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C329" s="3">
         <v>0.36842105263157898</v>
@@ -6118,272 +6543,272 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBBAD8A1-36CB-4B13-8017-EABCFFC1569A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>14.899999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>20.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>26.1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>31.700000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>37.300000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>37.299999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>42.900000000000006</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>42.900000000000013</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>48.500000000000007</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>54.100000000000009</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>59.700000000000017</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>65.300000000000011</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>70.900000000000006</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>76.5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>82.1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>87.699999999999989</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>93.299999999999983</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>98.899999999999977</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="B18">
-        <v>104.49999999999997</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>104.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="B19">
-        <v>110.09999999999997</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>110.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="B20">
-        <v>115.69999999999996</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>115.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>19.2</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="B22">
-        <v>26.599999999999994</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26.599999999999991</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="B24">
         <v>41.4</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="B25">
         <v>48.8</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>56.199999999999989</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="B27">
-        <v>63.599999999999994</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>63.599999999999987</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>78.400000000000006</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="B30">
         <v>85.800000000000011</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="B31">
         <v>93.200000000000017</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="B32">
-        <v>100.60000000000002</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>100.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="B33">
-        <v>108.00000000000003</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -6392,275 +6817,679 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D80D65-980E-42A9-AD93-08398CB603B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>17.2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>22.799999999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>28.4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>39.6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>45.2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>50.800000000000004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>56.400000000000006</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>56.400000000000013</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>62.000000000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>67.600000000000009</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>73.2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>78.8</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>84.399999999999991</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>89.999999999999986</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>95.59999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="B17">
-        <v>101.19999999999997</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>101.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="B18">
-        <v>106.79999999999997</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>106.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="B19">
-        <v>112.39999999999996</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>112.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="B20">
-        <v>117.99999999999996</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="B22">
         <v>26.4</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="B24">
-        <v>41.199999999999996</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="B25">
-        <v>48.599999999999994</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48.599999999999987</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>55.999999999999993</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>63.399999999999991</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>70.8</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>78.2</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="B30">
         <v>85.600000000000009</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="B31">
         <v>93.000000000000014</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="B32">
-        <v>100.40000000000002</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>100.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="B33">
-        <v>107.80000000000003</v>
+        <v>107.8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="78" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="5">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="5">
+        <v>5.4</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="5">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B9" s="5">
+        <v>7.4</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="5">
+        <v>7.4</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" s="5">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B17" s="5">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B18" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B19" s="5">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B20" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B21" s="5">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" s="5">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="5">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" s="5">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" s="5">
+        <v>14.9</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="5">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B27" s="5">
+        <v>2</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" s="5">
+        <v>15</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" s="5">
+        <v>3</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>